--- a/test/fixtures/order-imports/external-link.xlsx
+++ b/test/fixtures/order-imports/external-link.xlsx
@@ -37,11 +37,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="6">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="60" formatCode="00000000000"/>
     <numFmt numFmtId="61" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="62" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="63" formatCode="hh:mm"/>
-    <numFmt numFmtId="64" formatCode="00000000000"/>
+    <numFmt numFmtId="62" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="63" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="64" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="1">
     <font>
